--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>49000</t>
   </si>
@@ -70,6 +70,12 @@
     <t>436786</t>
   </si>
   <si>
+    <t>571940</t>
+  </si>
+  <si>
+    <t>571941</t>
+  </si>
+  <si>
     <t>436787</t>
   </si>
   <si>
@@ -106,6 +112,12 @@
     <t>Número total de participantes</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de participantes mujeres</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Total de participantes hombres</t>
+  </si>
+  <si>
     <t>Respuesta del sujeto obligado a los resultados, descripción sintética de lo que se tomó en cuenta</t>
   </si>
   <si>
@@ -121,31 +133,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Ver nota</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>6FFB4E6DABFD739345D1C8D47BEFE971</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Ver  nota</t>
-  </si>
-  <si>
-    <t>11/04/2022</t>
-  </si>
-  <si>
-    <t>Del periodo 01/04/2022 al 30/06/2022 en esta Subdirección de Actividades Paraescolares se encuentra impedida para reportar los mecanismos de participación ciudadana consagradas en el artículo XXXVII, toda vez que dentro del objeto del organismo público desconcentrado, Colegio de Bachilleres del estado de Tlaxcala no se encuentra dentro de su objeto desarrollar este tipo de actividades.</t>
+    <t>4CC906916205B6E1D0B17E98D92D9418</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>07/07/2023</t>
+  </si>
+  <si>
+    <t>Del periodo 01/04/2023 al 30/06/2023 en esta Subdirección de Actividades Paraescolares se encuentra impedida para reportar los mecanismos de participación ciudadana consagradas en el artículo XXXVII, toda vez que dentro del objeto del organismo público desconcentrado, Colegio de Bachilleres del estado de Tlaxcala no se encuentra dentro de su objeto desarrollar este tipo de actividades.</t>
   </si>
 </sst>
 </file>
@@ -222,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -236,9 +245,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,29 +547,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="82.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="255" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="82.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -580,7 +587,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -595,7 +602,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -615,22 +622,28 @@
         <v>9</v>
       </c>
       <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>8</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>7</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -664,10 +677,16 @@
       <c r="L5" t="s">
         <v>22</v>
       </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -680,83 +699,97 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A6:N6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
